--- a/tame_output/ON/bt/strategyON_20230814.xlsx
+++ b/tame_output/ON/bt/strategyON_20230814.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.1%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>102.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>139.8%</t>
+          <t>139.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>134.3%</t>
+          <t>134.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1688"/>
+  <dimension ref="A1:G1689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40334,7 +40334,7 @@
         <v>45150</v>
       </c>
       <c r="B1688" t="n">
-        <v>2.886032386438556</v>
+        <v>2.886140202013383</v>
       </c>
       <c r="C1688" t="n">
         <v>2.989821863634327</v>
@@ -40350,6 +40350,29 @@
       </c>
       <c r="G1688" t="n">
         <v>4.292250847506073</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="2" t="n">
+        <v>45151</v>
+      </c>
+      <c r="B1689" t="n">
+        <v>2.885475315628732</v>
+      </c>
+      <c r="C1689" t="n">
+        <v>2.98583653611852</v>
+      </c>
+      <c r="D1689" t="n">
+        <v>1.545200468742815</v>
+      </c>
+      <c r="E1689" t="n">
+        <v>3.603560299301899</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>2.173348398319916</v>
+      </c>
+      <c r="G1689" t="n">
+        <v>4.289845575110472</v>
       </c>
     </row>
   </sheetData>
